--- a/uploads/orchid petal.xlsx
+++ b/uploads/orchid petal.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="1167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="1174">
   <si>
     <t>Tower No.</t>
   </si>
@@ -3526,6 +3526,27 @@
   </si>
   <si>
     <t>no ava</t>
+  </si>
+  <si>
+    <t>call back</t>
+  </si>
+  <si>
+    <t>entres but abhi nhi</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>not  ava</t>
+  </si>
+  <si>
+    <t>out of serise</t>
+  </si>
+  <si>
+    <t>salet ou</t>
+  </si>
+  <si>
+    <t>entres but let sale</t>
   </si>
 </sst>
 </file>
@@ -7366,6 +7387,9 @@
       <c r="E182" s="1" t="s">
         <v>759</v>
       </c>
+      <c r="F182" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
@@ -7383,6 +7407,9 @@
       <c r="E183" s="1" t="s">
         <v>760</v>
       </c>
+      <c r="F183" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
@@ -7400,6 +7427,9 @@
       <c r="E184" s="1" t="s">
         <v>761</v>
       </c>
+      <c r="F184" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
@@ -7417,6 +7447,9 @@
       <c r="E185" s="1" t="s">
         <v>762</v>
       </c>
+      <c r="F185" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
@@ -7451,6 +7484,9 @@
       <c r="E187" s="1" t="s">
         <v>763</v>
       </c>
+      <c r="F187" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
@@ -7468,6 +7504,9 @@
       <c r="E188" s="1" t="s">
         <v>764</v>
       </c>
+      <c r="F188" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
@@ -7502,6 +7541,9 @@
       <c r="E190" s="1" t="s">
         <v>766</v>
       </c>
+      <c r="F190" t="s" s="0">
+        <v>1144</v>
+      </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
@@ -7519,6 +7561,9 @@
       <c r="E191" s="1" t="s">
         <v>767</v>
       </c>
+      <c r="F191" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
@@ -7536,6 +7581,9 @@
       <c r="E192" s="1" t="s">
         <v>768</v>
       </c>
+      <c r="F192" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
@@ -7570,6 +7618,9 @@
       <c r="E194" s="1" t="s">
         <v>770</v>
       </c>
+      <c r="F194" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
@@ -7604,6 +7655,9 @@
       <c r="E196" s="1" t="s">
         <v>772</v>
       </c>
+      <c r="F196" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
@@ -7621,6 +7675,9 @@
       <c r="E197" s="1" t="s">
         <v>773</v>
       </c>
+      <c r="F197" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
@@ -7638,6 +7695,9 @@
       <c r="E198" s="1" t="s">
         <v>774</v>
       </c>
+      <c r="F198" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
@@ -7655,6 +7715,9 @@
       <c r="E199" s="1" t="s">
         <v>775</v>
       </c>
+      <c r="F199" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
@@ -7672,6 +7735,9 @@
       <c r="E200" s="1" t="s">
         <v>776</v>
       </c>
+      <c r="F200" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
@@ -7689,6 +7755,9 @@
       <c r="E201" s="1" t="s">
         <v>777</v>
       </c>
+      <c r="F201" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
@@ -7706,6 +7775,9 @@
       <c r="E202" s="1" t="s">
         <v>778</v>
       </c>
+      <c r="F202" t="s" s="0">
+        <v>1167</v>
+      </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
@@ -7723,6 +7795,9 @@
       <c r="E203" s="1" t="s">
         <v>779</v>
       </c>
+      <c r="F203" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
@@ -7774,6 +7849,9 @@
       <c r="E206" s="1" t="s">
         <v>782</v>
       </c>
+      <c r="F206" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
@@ -7791,6 +7869,9 @@
       <c r="E207" s="1" t="s">
         <v>783</v>
       </c>
+      <c r="F207" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
@@ -7808,6 +7889,9 @@
       <c r="E208" s="1" t="s">
         <v>784</v>
       </c>
+      <c r="F208" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
@@ -7825,6 +7909,9 @@
       <c r="E209" s="1" t="s">
         <v>785</v>
       </c>
+      <c r="F209" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
@@ -7842,6 +7929,9 @@
       <c r="E210" s="1" t="s">
         <v>786</v>
       </c>
+      <c r="F210" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
@@ -7859,6 +7949,9 @@
       <c r="E211" s="1" t="s">
         <v>787</v>
       </c>
+      <c r="F211" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
@@ -7876,6 +7969,9 @@
       <c r="E212" s="1" t="s">
         <v>788</v>
       </c>
+      <c r="F212" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
@@ -7893,6 +7989,9 @@
       <c r="E213" s="1" t="s">
         <v>789</v>
       </c>
+      <c r="F213" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
@@ -7927,6 +8026,9 @@
       <c r="E215" s="1" t="s">
         <v>791</v>
       </c>
+      <c r="F215" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
@@ -7944,6 +8046,9 @@
       <c r="E216" s="1" t="s">
         <v>792</v>
       </c>
+      <c r="F216" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
@@ -7961,6 +8066,9 @@
       <c r="E217" s="1" t="s">
         <v>793</v>
       </c>
+      <c r="F217" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
@@ -7978,6 +8086,9 @@
       <c r="E218" s="1" t="s">
         <v>794</v>
       </c>
+      <c r="F218" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
@@ -7995,6 +8106,9 @@
       <c r="E219" s="1" t="s">
         <v>795</v>
       </c>
+      <c r="F219" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
@@ -8012,6 +8126,9 @@
       <c r="E220" s="1" t="s">
         <v>796</v>
       </c>
+      <c r="F220" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
@@ -8029,6 +8146,9 @@
       <c r="E221" s="1" t="s">
         <v>797</v>
       </c>
+      <c r="F221" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
@@ -8063,6 +8183,9 @@
       <c r="E223" s="1" t="s">
         <v>799</v>
       </c>
+      <c r="F223" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
@@ -8080,6 +8203,9 @@
       <c r="E224" s="1" t="s">
         <v>800</v>
       </c>
+      <c r="F224" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
@@ -8097,6 +8223,9 @@
       <c r="E225" s="1" t="s">
         <v>801</v>
       </c>
+      <c r="F225" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
@@ -8114,6 +8243,9 @@
       <c r="E226" s="1" t="s">
         <v>802</v>
       </c>
+      <c r="F226" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
@@ -8148,6 +8280,9 @@
       <c r="E228" s="1" t="s">
         <v>804</v>
       </c>
+      <c r="F228" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
@@ -8182,6 +8317,9 @@
       <c r="E230" s="1" t="s">
         <v>806</v>
       </c>
+      <c r="F230" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
@@ -8216,6 +8354,9 @@
       <c r="E232" s="1" t="s">
         <v>808</v>
       </c>
+      <c r="F232" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
@@ -8233,6 +8374,9 @@
       <c r="E233" s="1" t="s">
         <v>809</v>
       </c>
+      <c r="F233" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
@@ -8250,6 +8394,9 @@
       <c r="E234" s="1" t="s">
         <v>810</v>
       </c>
+      <c r="F234" t="s" s="0">
+        <v>1146</v>
+      </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
@@ -8267,6 +8414,9 @@
       <c r="E235" s="1" t="s">
         <v>811</v>
       </c>
+      <c r="F235" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
@@ -8284,6 +8434,9 @@
       <c r="E236" s="1" t="s">
         <v>812</v>
       </c>
+      <c r="F236" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
@@ -8301,6 +8454,9 @@
       <c r="E237" s="1" t="s">
         <v>813</v>
       </c>
+      <c r="F237" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
@@ -8335,6 +8491,9 @@
       <c r="E239" s="1" t="s">
         <v>815</v>
       </c>
+      <c r="F239" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
@@ -8352,6 +8511,9 @@
       <c r="E240" s="1" t="s">
         <v>816</v>
       </c>
+      <c r="F240" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
@@ -8386,6 +8548,9 @@
       <c r="E242" s="1" t="s">
         <v>817</v>
       </c>
+      <c r="F242" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
@@ -8454,6 +8619,9 @@
       <c r="E246" s="1" t="s">
         <v>818</v>
       </c>
+      <c r="F246" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
@@ -8471,6 +8639,9 @@
       <c r="E247" s="1" t="s">
         <v>819</v>
       </c>
+      <c r="F247" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
@@ -8488,6 +8659,9 @@
       <c r="E248" s="1" t="s">
         <v>820</v>
       </c>
+      <c r="F248" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
@@ -8505,6 +8679,9 @@
       <c r="E249" s="1" t="s">
         <v>821</v>
       </c>
+      <c r="F249" t="s" s="0">
+        <v>1168</v>
+      </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
@@ -8522,6 +8699,9 @@
       <c r="E250" s="1" t="s">
         <v>822</v>
       </c>
+      <c r="F250" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
@@ -8539,6 +8719,9 @@
       <c r="E251" s="1" t="s">
         <v>823</v>
       </c>
+      <c r="F251" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
@@ -8556,6 +8739,9 @@
       <c r="E252" s="1" t="s">
         <v>824</v>
       </c>
+      <c r="F252" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
@@ -8573,6 +8759,9 @@
       <c r="E253" s="1" t="s">
         <v>825</v>
       </c>
+      <c r="F253" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
@@ -8607,6 +8796,9 @@
       <c r="E255" s="1" t="s">
         <v>827</v>
       </c>
+      <c r="F255" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
@@ -8624,6 +8816,9 @@
       <c r="E256" s="1" t="s">
         <v>828</v>
       </c>
+      <c r="F256" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
@@ -8658,6 +8853,9 @@
       <c r="E258" s="1" t="s">
         <v>830</v>
       </c>
+      <c r="F258" t="s" s="0">
+        <v>1146</v>
+      </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
@@ -8675,6 +8873,9 @@
       <c r="E259" s="1" t="s">
         <v>831</v>
       </c>
+      <c r="F259" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
@@ -8726,6 +8927,9 @@
       <c r="E262" s="1" t="s">
         <v>834</v>
       </c>
+      <c r="F262" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
@@ -8743,6 +8947,9 @@
       <c r="E263" s="1" t="s">
         <v>835</v>
       </c>
+      <c r="F263" t="s" s="0">
+        <v>1144</v>
+      </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
@@ -8760,6 +8967,9 @@
       <c r="E264" s="1" t="s">
         <v>836</v>
       </c>
+      <c r="F264" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
@@ -8777,6 +8987,9 @@
       <c r="E265" s="1" t="s">
         <v>837</v>
       </c>
+      <c r="F265" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
@@ -8794,6 +9007,9 @@
       <c r="E266" s="1" t="s">
         <v>838</v>
       </c>
+      <c r="F266" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
@@ -8811,6 +9027,9 @@
       <c r="E267" s="1" t="s">
         <v>839</v>
       </c>
+      <c r="F267" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
@@ -8828,6 +9047,9 @@
       <c r="E268" s="1" t="s">
         <v>840</v>
       </c>
+      <c r="F268" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
@@ -8845,6 +9067,9 @@
       <c r="E269" s="1" t="s">
         <v>841</v>
       </c>
+      <c r="F269" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
@@ -8879,6 +9104,9 @@
       <c r="E271" s="1" t="s">
         <v>843</v>
       </c>
+      <c r="F271" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
@@ -8896,6 +9124,9 @@
       <c r="E272" s="1" t="s">
         <v>844</v>
       </c>
+      <c r="F272" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
@@ -8913,6 +9144,9 @@
       <c r="E273" s="1" t="s">
         <v>845</v>
       </c>
+      <c r="F273" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
@@ -8930,6 +9164,9 @@
       <c r="E274" s="1" t="s">
         <v>846</v>
       </c>
+      <c r="F274" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
@@ -8947,6 +9184,9 @@
       <c r="E275" s="1" t="s">
         <v>847</v>
       </c>
+      <c r="F275" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
@@ -8981,6 +9221,9 @@
       <c r="E277" s="1" t="s">
         <v>849</v>
       </c>
+      <c r="F277" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
@@ -8998,6 +9241,9 @@
       <c r="E278" s="1" t="s">
         <v>850</v>
       </c>
+      <c r="F278" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
@@ -9013,7 +9259,10 @@
         <v>2337</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>851</v>
+        <v>695</v>
+      </c>
+      <c r="F279" t="s" s="0">
+        <v>1149</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
@@ -9032,6 +9281,9 @@
       <c r="E280" s="1" t="s">
         <v>852</v>
       </c>
+      <c r="F280" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
@@ -9049,6 +9301,9 @@
       <c r="E281" s="1" t="s">
         <v>853</v>
       </c>
+      <c r="F281" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
@@ -9066,6 +9321,9 @@
       <c r="E282" s="1" t="s">
         <v>854</v>
       </c>
+      <c r="F282" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
@@ -9100,6 +9358,9 @@
       <c r="E284" s="1" t="s">
         <v>856</v>
       </c>
+      <c r="F284" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
@@ -9117,6 +9378,9 @@
       <c r="E285" s="1" t="s">
         <v>857</v>
       </c>
+      <c r="F285" t="s" s="0">
+        <v>1146</v>
+      </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
@@ -9134,6 +9398,9 @@
       <c r="E286" s="1" t="s">
         <v>858</v>
       </c>
+      <c r="F286" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
@@ -9151,6 +9418,9 @@
       <c r="E287" s="1" t="s">
         <v>859</v>
       </c>
+      <c r="F287" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
@@ -9168,6 +9438,9 @@
       <c r="E288" s="1" t="s">
         <v>860</v>
       </c>
+      <c r="F288" t="s" s="0">
+        <v>1170</v>
+      </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
@@ -9185,6 +9458,9 @@
       <c r="E289" s="1" t="s">
         <v>861</v>
       </c>
+      <c r="F289" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
@@ -9202,6 +9478,9 @@
       <c r="E290" s="1" t="s">
         <v>862</v>
       </c>
+      <c r="F290" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
@@ -9219,6 +9498,9 @@
       <c r="E291" s="4">
         <v>9.8710011909870993E+19</v>
       </c>
+      <c r="F291" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
@@ -9236,6 +9518,9 @@
       <c r="E292" s="1">
         <v>9810704589</v>
       </c>
+      <c r="F292" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
@@ -9287,6 +9572,9 @@
       <c r="E295" s="1" t="s">
         <v>865</v>
       </c>
+      <c r="F295" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
@@ -9304,6 +9592,9 @@
       <c r="E296" s="1" t="s">
         <v>866</v>
       </c>
+      <c r="F296" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
@@ -9355,6 +9646,9 @@
       <c r="E299" s="1" t="s">
         <v>868</v>
       </c>
+      <c r="F299" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
@@ -9372,6 +9666,9 @@
       <c r="E300" s="1" t="s">
         <v>869</v>
       </c>
+      <c r="F300" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
@@ -9389,6 +9686,9 @@
       <c r="E301" s="1" t="s">
         <v>870</v>
       </c>
+      <c r="F301" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
@@ -9406,6 +9706,9 @@
       <c r="E302" s="1" t="s">
         <v>871</v>
       </c>
+      <c r="F302" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
@@ -9423,6 +9726,9 @@
       <c r="E303" s="1" t="s">
         <v>872</v>
       </c>
+      <c r="F303" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
@@ -9440,6 +9746,9 @@
       <c r="E304" s="1" t="s">
         <v>873</v>
       </c>
+      <c r="F304" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
@@ -9457,6 +9766,9 @@
       <c r="E305" s="1" t="s">
         <v>874</v>
       </c>
+      <c r="F305" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
@@ -9491,6 +9803,9 @@
       <c r="E307" s="1" t="s">
         <v>875</v>
       </c>
+      <c r="F307" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
@@ -9508,6 +9823,9 @@
       <c r="E308" s="1" t="s">
         <v>876</v>
       </c>
+      <c r="F308" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
@@ -9542,6 +9860,9 @@
       <c r="E310" s="1" t="s">
         <v>878</v>
       </c>
+      <c r="F310" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
@@ -9559,6 +9880,9 @@
       <c r="E311" s="1" t="s">
         <v>879</v>
       </c>
+      <c r="F311" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
@@ -9576,6 +9900,9 @@
       <c r="E312" s="1" t="s">
         <v>880</v>
       </c>
+      <c r="F312" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
@@ -9593,6 +9920,9 @@
       <c r="E313" s="1" t="s">
         <v>881</v>
       </c>
+      <c r="F313" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
@@ -9627,6 +9957,9 @@
       <c r="E315" s="1" t="s">
         <v>883</v>
       </c>
+      <c r="F315" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
@@ -9678,6 +10011,9 @@
       <c r="E318" s="1" t="s">
         <v>886</v>
       </c>
+      <c r="F318" t="s" s="0">
+        <v>1146</v>
+      </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
@@ -9695,6 +10031,9 @@
       <c r="E319" s="1" t="s">
         <v>887</v>
       </c>
+      <c r="F319" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
@@ -9729,6 +10068,9 @@
       <c r="E321" s="1" t="s">
         <v>888</v>
       </c>
+      <c r="F321" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
@@ -9763,6 +10105,9 @@
       <c r="E323" s="1" t="s">
         <v>890</v>
       </c>
+      <c r="F323" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
@@ -9780,6 +10125,9 @@
       <c r="E324" s="1" t="s">
         <v>891</v>
       </c>
+      <c r="F324" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
@@ -9797,6 +10145,9 @@
       <c r="E325" s="1" t="s">
         <v>892</v>
       </c>
+      <c r="F325" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
@@ -9831,6 +10182,9 @@
       <c r="E327" s="1" t="s">
         <v>893</v>
       </c>
+      <c r="F327" t="s" s="0">
+        <v>1159</v>
+      </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
@@ -9848,6 +10202,9 @@
       <c r="E328" s="1" t="s">
         <v>894</v>
       </c>
+      <c r="F328" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
@@ -9865,6 +10222,9 @@
       <c r="E329" s="1" t="s">
         <v>895</v>
       </c>
+      <c r="F329" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
@@ -9882,6 +10242,9 @@
       <c r="E330" s="1" t="s">
         <v>896</v>
       </c>
+      <c r="F330" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
@@ -9899,6 +10262,9 @@
       <c r="E331" s="1" t="s">
         <v>897</v>
       </c>
+      <c r="F331" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
@@ -9916,6 +10282,9 @@
       <c r="E332" s="1" t="s">
         <v>898</v>
       </c>
+      <c r="F332" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
@@ -9933,6 +10302,9 @@
       <c r="E333" s="1" t="s">
         <v>899</v>
       </c>
+      <c r="F333" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
@@ -9950,6 +10322,9 @@
       <c r="E334" s="1" t="s">
         <v>900</v>
       </c>
+      <c r="F334" t="s" s="0">
+        <v>1171</v>
+      </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
@@ -9967,6 +10342,9 @@
       <c r="E335" s="1" t="s">
         <v>901</v>
       </c>
+      <c r="F335" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
@@ -9984,6 +10362,9 @@
       <c r="E336" s="1" t="s">
         <v>902</v>
       </c>
+      <c r="F336" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
@@ -10018,6 +10399,9 @@
       <c r="E338" s="1" t="s">
         <v>904</v>
       </c>
+      <c r="F338" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
@@ -10052,6 +10436,9 @@
       <c r="E340" s="1" t="s">
         <v>905</v>
       </c>
+      <c r="F340" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
@@ -10069,6 +10456,9 @@
       <c r="E341" s="1" t="s">
         <v>906</v>
       </c>
+      <c r="F341" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
@@ -10103,6 +10493,9 @@
       <c r="E343" s="1" t="s">
         <v>908</v>
       </c>
+      <c r="F343" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
@@ -10120,6 +10513,9 @@
       <c r="E344" s="1" t="s">
         <v>909</v>
       </c>
+      <c r="F344" t="s" s="0">
+        <v>1151</v>
+      </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
@@ -10137,6 +10533,9 @@
       <c r="E345" s="1" t="s">
         <v>910</v>
       </c>
+      <c r="F345" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
@@ -10154,6 +10553,9 @@
       <c r="E346" s="1" t="s">
         <v>911</v>
       </c>
+      <c r="F346" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
@@ -10171,6 +10573,9 @@
       <c r="E347" s="1" t="s">
         <v>912</v>
       </c>
+      <c r="F347" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
@@ -10188,6 +10593,9 @@
       <c r="E348" s="1" t="s">
         <v>913</v>
       </c>
+      <c r="F348" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
@@ -10205,6 +10613,9 @@
       <c r="E349" s="1" t="s">
         <v>914</v>
       </c>
+      <c r="F349" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
@@ -10222,6 +10633,9 @@
       <c r="E350" s="1" t="s">
         <v>915</v>
       </c>
+      <c r="F350" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
@@ -10239,6 +10653,9 @@
       <c r="E351" s="1" t="s">
         <v>916</v>
       </c>
+      <c r="F351" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
@@ -10273,6 +10690,9 @@
       <c r="E353" s="1" t="s">
         <v>918</v>
       </c>
+      <c r="F353" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
@@ -10290,6 +10710,9 @@
       <c r="E354" s="1" t="s">
         <v>919</v>
       </c>
+      <c r="F354" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
@@ -10307,6 +10730,9 @@
       <c r="E355" s="1" t="s">
         <v>920</v>
       </c>
+      <c r="F355" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
@@ -10324,6 +10750,9 @@
       <c r="E356" s="1" t="s">
         <v>921</v>
       </c>
+      <c r="F356" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
@@ -10341,6 +10770,9 @@
       <c r="E357" s="1" t="s">
         <v>922</v>
       </c>
+      <c r="F357" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
@@ -10358,6 +10790,9 @@
       <c r="E358" s="1" t="s">
         <v>923</v>
       </c>
+      <c r="F358" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
@@ -10375,6 +10810,9 @@
       <c r="E359" s="1" t="s">
         <v>924</v>
       </c>
+      <c r="F359" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
@@ -10392,6 +10830,9 @@
       <c r="E360" s="1" t="s">
         <v>925</v>
       </c>
+      <c r="F360" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
@@ -10426,6 +10867,9 @@
       <c r="E362" s="1" t="s">
         <v>927</v>
       </c>
+      <c r="F362" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
@@ -10443,6 +10887,9 @@
       <c r="E363" s="1" t="s">
         <v>928</v>
       </c>
+      <c r="F363" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
@@ -10460,6 +10907,9 @@
       <c r="E364" s="1" t="s">
         <v>929</v>
       </c>
+      <c r="F364" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
@@ -10477,6 +10927,9 @@
       <c r="E365" s="1" t="s">
         <v>930</v>
       </c>
+      <c r="F365" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
@@ -10511,6 +10964,9 @@
       <c r="E367" s="1" t="s">
         <v>931</v>
       </c>
+      <c r="F367" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
@@ -10528,6 +10984,9 @@
       <c r="E368" s="1" t="s">
         <v>932</v>
       </c>
+      <c r="F368" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
@@ -10545,6 +11004,9 @@
       <c r="E369" s="1" t="s">
         <v>933</v>
       </c>
+      <c r="F369" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
@@ -10579,6 +11041,9 @@
       <c r="E371" s="1" t="s">
         <v>935</v>
       </c>
+      <c r="F371" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
@@ -10596,6 +11061,9 @@
       <c r="E372" s="1" t="s">
         <v>936</v>
       </c>
+      <c r="F372" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
@@ -10630,6 +11098,9 @@
       <c r="E374" s="4">
         <v>2.745291298111E+17</v>
       </c>
+      <c r="F374" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
@@ -10647,6 +11118,9 @@
       <c r="E375" s="1" t="s">
         <v>938</v>
       </c>
+      <c r="F375" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
@@ -10664,6 +11138,9 @@
       <c r="E376" s="1" t="s">
         <v>939</v>
       </c>
+      <c r="F376" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
@@ -10681,6 +11158,9 @@
       <c r="E377" s="1" t="s">
         <v>940</v>
       </c>
+      <c r="F377" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
@@ -10715,6 +11195,9 @@
       <c r="E379" s="1" t="s">
         <v>941</v>
       </c>
+      <c r="F379" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
@@ -10732,6 +11215,9 @@
       <c r="E380" s="1" t="s">
         <v>942</v>
       </c>
+      <c r="F380" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
@@ -10749,6 +11235,9 @@
       <c r="E381" s="1" t="s">
         <v>943</v>
       </c>
+      <c r="F381" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
@@ -10766,6 +11255,9 @@
       <c r="E382" s="1" t="s">
         <v>944</v>
       </c>
+      <c r="F382" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
@@ -10800,6 +11292,9 @@
       <c r="E384" s="1" t="s">
         <v>945</v>
       </c>
+      <c r="F384" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
@@ -10817,6 +11312,9 @@
       <c r="E385" s="1" t="s">
         <v>946</v>
       </c>
+      <c r="F385" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
@@ -10834,6 +11332,9 @@
       <c r="E386" s="1">
         <v>9431075303</v>
       </c>
+      <c r="F386" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
@@ -10851,6 +11352,9 @@
       <c r="E387" s="1" t="s">
         <v>947</v>
       </c>
+      <c r="F387" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
@@ -10868,6 +11372,9 @@
       <c r="E388" s="1" t="s">
         <v>948</v>
       </c>
+      <c r="F388" t="s" s="0">
+        <v>1146</v>
+      </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
@@ -10885,6 +11392,9 @@
       <c r="E389" s="1" t="s">
         <v>949</v>
       </c>
+      <c r="F389" t="s" s="0">
+        <v>1146</v>
+      </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
@@ -10902,6 +11412,9 @@
       <c r="E390" s="1" t="s">
         <v>950</v>
       </c>
+      <c r="F390" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
@@ -10919,6 +11432,9 @@
       <c r="E391" s="1" t="s">
         <v>951</v>
       </c>
+      <c r="F391" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
@@ -10936,6 +11452,9 @@
       <c r="E392" s="1" t="s">
         <v>952</v>
       </c>
+      <c r="F392" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
@@ -10953,6 +11472,9 @@
       <c r="E393" s="1" t="s">
         <v>953</v>
       </c>
+      <c r="F393" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
@@ -10987,6 +11509,9 @@
       <c r="E395" s="1" t="s">
         <v>954</v>
       </c>
+      <c r="F395" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
@@ -11004,6 +11529,9 @@
       <c r="E396" s="1" t="s">
         <v>955</v>
       </c>
+      <c r="F396" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
@@ -11021,6 +11549,9 @@
       <c r="E397" s="1" t="s">
         <v>956</v>
       </c>
+      <c r="F397" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
@@ -11038,6 +11569,9 @@
       <c r="E398" s="1" t="s">
         <v>957</v>
       </c>
+      <c r="F398" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
@@ -11072,6 +11606,9 @@
       <c r="E400" s="1" t="s">
         <v>958</v>
       </c>
+      <c r="F400" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
@@ -11106,6 +11643,9 @@
       <c r="E402" s="1" t="s">
         <v>960</v>
       </c>
+      <c r="F402" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
@@ -11140,6 +11680,9 @@
       <c r="E404" s="1" t="s">
         <v>962</v>
       </c>
+      <c r="F404" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
@@ -11174,6 +11717,9 @@
       <c r="E406" s="1" t="s">
         <v>964</v>
       </c>
+      <c r="F406" t="s" s="0">
+        <v>1173</v>
+      </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
@@ -11225,6 +11771,9 @@
       <c r="E409" s="1" t="s">
         <v>966</v>
       </c>
+      <c r="F409" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
@@ -11259,6 +11808,9 @@
       <c r="E411" s="1" t="s">
         <v>967</v>
       </c>
+      <c r="F411" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
@@ -11276,6 +11828,9 @@
       <c r="E412" s="1" t="s">
         <v>968</v>
       </c>
+      <c r="F412" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
@@ -11310,6 +11865,9 @@
       <c r="E414" s="1" t="s">
         <v>970</v>
       </c>
+      <c r="F414" t="s" s="0">
+        <v>1146</v>
+      </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
@@ -11327,6 +11885,9 @@
       <c r="E415" s="1" t="s">
         <v>971</v>
       </c>
+      <c r="F415" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
@@ -11344,6 +11905,9 @@
       <c r="E416" s="1" t="s">
         <v>972</v>
       </c>
+      <c r="F416" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
@@ -11361,6 +11925,9 @@
       <c r="E417" s="1" t="s">
         <v>973</v>
       </c>
+      <c r="F417" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
@@ -11378,6 +11945,9 @@
       <c r="E418" s="1" t="s">
         <v>974</v>
       </c>
+      <c r="F418" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
@@ -11429,6 +11999,9 @@
       <c r="E421" s="1" t="s">
         <v>977</v>
       </c>
+      <c r="F421" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
@@ -11446,6 +12019,9 @@
       <c r="E422" s="1" t="s">
         <v>978</v>
       </c>
+      <c r="F422" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
@@ -11480,6 +12056,9 @@
       <c r="E424" s="1" t="s">
         <v>980</v>
       </c>
+      <c r="F424" t="s" s="0">
+        <v>1146</v>
+      </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
@@ -11514,6 +12093,9 @@
       <c r="E426" s="1" t="s">
         <v>982</v>
       </c>
+      <c r="F426" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
@@ -11531,6 +12113,9 @@
       <c r="E427" s="1" t="s">
         <v>983</v>
       </c>
+      <c r="F427" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" s="1">
@@ -11548,6 +12133,9 @@
       <c r="E428" s="1" t="s">
         <v>984</v>
       </c>
+      <c r="F428" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
@@ -11565,6 +12153,9 @@
       <c r="E429" s="1" t="s">
         <v>985</v>
       </c>
+      <c r="F429" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
@@ -11582,6 +12173,9 @@
       <c r="E430" s="1" t="s">
         <v>986</v>
       </c>
+      <c r="F430" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
@@ -11616,6 +12210,9 @@
       <c r="E432" s="1" t="s">
         <v>988</v>
       </c>
+      <c r="F432" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
@@ -11633,6 +12230,9 @@
       <c r="E433" s="1" t="s">
         <v>989</v>
       </c>
+      <c r="F433" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
@@ -11667,6 +12267,9 @@
       <c r="E435" s="1" t="s">
         <v>990</v>
       </c>
+      <c r="F435" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
@@ -11684,6 +12287,9 @@
       <c r="E436" s="1" t="s">
         <v>991</v>
       </c>
+      <c r="F436" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
@@ -11701,6 +12307,9 @@
       <c r="E437" s="1" t="s">
         <v>992</v>
       </c>
+      <c r="F437" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
@@ -11752,6 +12361,9 @@
       <c r="E440" s="1" t="s">
         <v>995</v>
       </c>
+      <c r="F440" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" s="1">
@@ -11769,6 +12381,9 @@
       <c r="E441" s="1" t="s">
         <v>996</v>
       </c>
+      <c r="F441" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" s="1">
@@ -11786,6 +12401,9 @@
       <c r="E442" s="1" t="s">
         <v>997</v>
       </c>
+      <c r="F442" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" s="1">
@@ -11820,6 +12438,9 @@
       <c r="E444" s="4">
         <v>1.1252685709818599E+19</v>
       </c>
+      <c r="F444" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" s="1">
@@ -11854,6 +12475,9 @@
       <c r="E446" s="1" t="s">
         <v>999</v>
       </c>
+      <c r="F446" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
@@ -11871,6 +12495,9 @@
       <c r="E447" s="1" t="s">
         <v>1000</v>
       </c>
+      <c r="F447" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" s="1">
@@ -11905,6 +12532,9 @@
       <c r="E449" s="1" t="s">
         <v>1001</v>
       </c>
+      <c r="F449" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" s="1">
@@ -11922,6 +12552,9 @@
       <c r="E450" s="1" t="s">
         <v>1002</v>
       </c>
+      <c r="F450" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" s="1">
@@ -11939,6 +12572,9 @@
       <c r="E451" s="1" t="s">
         <v>1003</v>
       </c>
+      <c r="F451" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" s="1">
@@ -11990,6 +12626,9 @@
       <c r="E454" s="1" t="s">
         <v>1005</v>
       </c>
+      <c r="F454" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" s="1">
@@ -12007,6 +12646,9 @@
       <c r="E455" s="1" t="s">
         <v>1006</v>
       </c>
+      <c r="F455" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
@@ -12024,6 +12666,9 @@
       <c r="E456" s="1" t="s">
         <v>1007</v>
       </c>
+      <c r="F456" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
@@ -12058,6 +12703,9 @@
       <c r="E458" s="1" t="s">
         <v>1009</v>
       </c>
+      <c r="F458" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
@@ -12075,6 +12723,9 @@
       <c r="E459" s="1" t="s">
         <v>1010</v>
       </c>
+      <c r="F459" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
@@ -12092,6 +12743,9 @@
       <c r="E460" s="1" t="s">
         <v>1011</v>
       </c>
+      <c r="F460" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
@@ -12109,6 +12763,9 @@
       <c r="E461" s="1" t="s">
         <v>1012</v>
       </c>
+      <c r="F461" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
@@ -12126,6 +12783,9 @@
       <c r="E462" s="1" t="s">
         <v>1013</v>
       </c>
+      <c r="F462" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
@@ -12143,6 +12803,9 @@
       <c r="E463" s="1" t="s">
         <v>1014</v>
       </c>
+      <c r="F463" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
@@ -12160,6 +12823,9 @@
       <c r="E464" s="1" t="s">
         <v>1015</v>
       </c>
+      <c r="F464" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
@@ -12177,6 +12843,9 @@
       <c r="E465" s="1" t="s">
         <v>1016</v>
       </c>
+      <c r="F465" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
@@ -12194,6 +12863,9 @@
       <c r="E466" s="1" t="s">
         <v>1017</v>
       </c>
+      <c r="F466" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
@@ -12211,6 +12883,9 @@
       <c r="E467" s="1" t="s">
         <v>1018</v>
       </c>
+      <c r="F467" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
@@ -12228,6 +12903,9 @@
       <c r="E468" s="1" t="s">
         <v>1019</v>
       </c>
+      <c r="F468" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" s="1">
@@ -12245,6 +12923,9 @@
       <c r="E469" s="1" t="s">
         <v>1020</v>
       </c>
+      <c r="F469" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" s="1">
@@ -12262,6 +12943,9 @@
       <c r="E470" s="1" t="s">
         <v>1021</v>
       </c>
+      <c r="F470" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" s="1">
@@ -12278,6 +12962,9 @@
       </c>
       <c r="E471" s="1" t="s">
         <v>1022</v>
+      </c>
+      <c r="F471" t="s" s="0">
+        <v>1142</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.3">

--- a/uploads/orchid petal.xlsx
+++ b/uploads/orchid petal.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="1177">
   <si>
     <t>Tower No.</t>
   </si>
@@ -3547,6 +3547,15 @@
   </si>
   <si>
     <t>entres but let sale</t>
+  </si>
+  <si>
+    <t>entres but late sale</t>
+  </si>
+  <si>
+    <t>no entres</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
@@ -5811,7 +5820,7 @@
         <v>687</v>
       </c>
       <c r="F100" t="s" s="0">
-        <v>1140</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -6011,7 +6020,7 @@
         <v>694</v>
       </c>
       <c r="F110" t="s" s="0">
-        <v>1162</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -7034,7 +7043,7 @@
         <v>742</v>
       </c>
       <c r="F164" t="s" s="0">
-        <v>1141</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
@@ -7071,7 +7080,7 @@
         <v>744</v>
       </c>
       <c r="F166" t="s" s="0">
-        <v>1142</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
@@ -7111,7 +7120,7 @@
         <v>746</v>
       </c>
       <c r="F168" t="s" s="0">
-        <v>1140</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
@@ -8355,7 +8364,7 @@
         <v>808</v>
       </c>
       <c r="F232" t="s" s="0">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
@@ -13102,6 +13111,9 @@
       <c r="E479" s="1">
         <v>9873934564</v>
       </c>
+      <c r="F479" t="s" s="0">
+        <v>1175</v>
+      </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" s="1">
@@ -13136,6 +13148,9 @@
       <c r="E481" s="1" t="s">
         <v>1030</v>
       </c>
+      <c r="F481" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" s="1">
@@ -13153,6 +13168,9 @@
       <c r="E482" s="1" t="s">
         <v>1031</v>
       </c>
+      <c r="F482" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" s="1">
@@ -13204,6 +13222,9 @@
       <c r="E485" s="1" t="s">
         <v>1033</v>
       </c>
+      <c r="F485" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
@@ -13221,6 +13242,9 @@
       <c r="E486" s="1" t="s">
         <v>1034</v>
       </c>
+      <c r="F486" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
@@ -13255,6 +13279,9 @@
       <c r="E488" s="1" t="s">
         <v>1036</v>
       </c>
+      <c r="F488" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" s="1">
@@ -13272,6 +13299,9 @@
       <c r="E489" s="1" t="s">
         <v>1037</v>
       </c>
+      <c r="F489" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
@@ -13289,6 +13319,9 @@
       <c r="E490" s="1" t="s">
         <v>1038</v>
       </c>
+      <c r="F490" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
@@ -13306,6 +13339,9 @@
       <c r="E491" s="1" t="s">
         <v>1039</v>
       </c>
+      <c r="F491" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" s="1">
@@ -13323,6 +13359,9 @@
       <c r="E492" s="1" t="s">
         <v>1040</v>
       </c>
+      <c r="F492" t="s" s="0">
+        <v>1146</v>
+      </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" s="1">
@@ -13340,6 +13379,9 @@
       <c r="E493" s="1" t="s">
         <v>1041</v>
       </c>
+      <c r="F493" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" s="1">
@@ -13357,6 +13399,9 @@
       <c r="E494" s="1" t="s">
         <v>1042</v>
       </c>
+      <c r="F494" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" s="1">
@@ -13374,6 +13419,9 @@
       <c r="E495" s="1" t="s">
         <v>1043</v>
       </c>
+      <c r="F495" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" s="1">
@@ -13391,6 +13439,9 @@
       <c r="E496" s="1" t="s">
         <v>1044</v>
       </c>
+      <c r="F496" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
@@ -13425,6 +13476,9 @@
       <c r="E498" s="1" t="s">
         <v>1046</v>
       </c>
+      <c r="F498" t="s" s="0">
+        <v>1174</v>
+      </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" s="1">
@@ -13442,6 +13496,9 @@
       <c r="E499" s="1" t="s">
         <v>1047</v>
       </c>
+      <c r="F499" t="s" s="0">
+        <v>1149</v>
+      </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" s="1">
@@ -13595,6 +13652,9 @@
       <c r="E508" s="1" t="s">
         <v>1056</v>
       </c>
+      <c r="F508" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509" s="1">
@@ -13697,6 +13757,9 @@
       <c r="E514" s="1" t="s">
         <v>1061</v>
       </c>
+      <c r="F514" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
@@ -13714,6 +13777,9 @@
       <c r="E515" s="1" t="s">
         <v>1062</v>
       </c>
+      <c r="F515" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
@@ -13867,6 +13933,9 @@
       <c r="E524" s="1" t="s">
         <v>1070</v>
       </c>
+      <c r="F524" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" s="1">
@@ -13884,6 +13953,9 @@
       <c r="E525" s="1" t="s">
         <v>1071</v>
       </c>
+      <c r="F525" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526" s="1">
@@ -13952,6 +14024,9 @@
       <c r="E529" s="1" t="s">
         <v>1074</v>
       </c>
+      <c r="F529" t="s" s="0">
+        <v>1144</v>
+      </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" s="1">
@@ -14190,6 +14265,9 @@
       <c r="E543" s="1" t="s">
         <v>1086</v>
       </c>
+      <c r="F543" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
@@ -14207,6 +14285,9 @@
       <c r="E544" s="1" t="s">
         <v>1087</v>
       </c>
+      <c r="F544" t="s" s="0">
+        <v>1148</v>
+      </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
@@ -14224,6 +14305,9 @@
       <c r="E545" s="1" t="s">
         <v>1088</v>
       </c>
+      <c r="F545" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
@@ -14394,6 +14478,9 @@
       <c r="E555" s="1" t="s">
         <v>1097</v>
       </c>
+      <c r="F555" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A556" s="1">
@@ -14479,6 +14566,9 @@
       <c r="E560" s="1" t="s">
         <v>1101</v>
       </c>
+      <c r="F560" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561" s="1">
@@ -14598,6 +14688,9 @@
       <c r="E567" s="1" t="s">
         <v>1108</v>
       </c>
+      <c r="F567" t="s" s="0">
+        <v>1141</v>
+      </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568" s="1">
@@ -14615,6 +14708,9 @@
       <c r="E568" s="1" t="s">
         <v>1109</v>
       </c>
+      <c r="F568" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" s="1">
@@ -14666,6 +14762,9 @@
       <c r="E571" s="1" t="s">
         <v>1112</v>
       </c>
+      <c r="F571" t="s" s="0">
+        <v>1145</v>
+      </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
@@ -14683,6 +14782,9 @@
       <c r="E572" s="1" t="s">
         <v>1113</v>
       </c>
+      <c r="F572" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573" s="1">
@@ -14887,6 +14989,9 @@
       <c r="E584" s="1" t="s">
         <v>1124</v>
       </c>
+      <c r="F584" t="s" s="0">
+        <v>1140</v>
+      </c>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
@@ -14921,6 +15026,9 @@
       <c r="E586" s="1" t="s">
         <v>1126</v>
       </c>
+      <c r="F586" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
@@ -15006,6 +15114,9 @@
       <c r="E591" s="1" t="s">
         <v>1130</v>
       </c>
+      <c r="F591" t="s" s="0">
+        <v>1147</v>
+      </c>
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592" s="1">
@@ -15057,6 +15168,9 @@
       <c r="E594" s="1" t="s">
         <v>1133</v>
       </c>
+      <c r="F594" t="s" s="0">
+        <v>1142</v>
+      </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
@@ -15073,6 +15187,9 @@
       </c>
       <c r="E595" s="1" t="s">
         <v>1134</v>
+      </c>
+      <c r="F595" t="s" s="0">
+        <v>1144</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.3">
